--- a/2026/Proyecto_Final/drive_proyecto_final/Técnico/Logistica de distribución.xlsx
+++ b/2026/Proyecto_Final/drive_proyecto_final/Técnico/Logistica de distribución.xlsx
@@ -63,39 +63,72 @@
     <t>A01</t>
   </si>
   <si>
+    <t>Chocolate con chips picante 150gr.</t>
+  </si>
+  <si>
+    <t>Gourmet</t>
+  </si>
+  <si>
     <t>[En M]</t>
   </si>
   <si>
-    <t>Chocolate con chips picante 150gr.</t>
-  </si>
-  <si>
-    <t>Gourmet</t>
+    <t>A02</t>
+  </si>
+  <si>
+    <t>Galletitas símil chocolinas free 150gr.</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>Galletitas símil chocolinas 150gr.</t>
+  </si>
+  <si>
+    <t>Clásicas</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>Pepas chocolate y batata 150gr.</t>
   </si>
   <si>
     <t>CHASIS 8 PALLETS</t>
   </si>
   <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>Bizcochos sabor queso free 150gr.</t>
+  </si>
+  <si>
+    <t>A06</t>
+  </si>
+  <si>
+    <t>Bizcochos sabor queso 150gr.</t>
+  </si>
+  <si>
     <t>AÑO 1</t>
   </si>
   <si>
-    <t>A02</t>
-  </si>
-  <si>
     <t>AÑO 2</t>
   </si>
   <si>
-    <t>Galletitas símil chocolinas free 150gr.</t>
-  </si>
-  <si>
     <t>AÑO 3</t>
   </si>
   <si>
-    <t>Free</t>
+    <t>A07</t>
   </si>
   <si>
     <t>AÑO 4</t>
   </si>
   <si>
+    <t>Polvorones free 150gr.</t>
+  </si>
+  <si>
     <t>AÑO 5</t>
   </si>
   <si>
@@ -117,51 +150,18 @@
     <t>Costos</t>
   </si>
   <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>Polvorones 150gr.</t>
+  </si>
+  <si>
     <t>Datos</t>
   </si>
   <si>
-    <t>A03</t>
-  </si>
-  <si>
-    <t>Galletitas símil chocolinas 150gr.</t>
-  </si>
-  <si>
     <t>Monto en pesos</t>
   </si>
   <si>
-    <t>Clásicas</t>
-  </si>
-  <si>
-    <t>A04</t>
-  </si>
-  <si>
-    <t>Pepas chocolate y batata 150gr.</t>
-  </si>
-  <si>
-    <t>A05</t>
-  </si>
-  <si>
-    <t>Bizcochos sabor queso free 150gr.</t>
-  </si>
-  <si>
-    <t>A06</t>
-  </si>
-  <si>
-    <t>Bizcochos sabor queso 150gr.</t>
-  </si>
-  <si>
-    <t>A07</t>
-  </si>
-  <si>
-    <t>Polvorones free 150gr.</t>
-  </si>
-  <si>
-    <t>A08</t>
-  </si>
-  <si>
-    <t>Polvorones 150gr.</t>
-  </si>
-  <si>
     <t>B01</t>
   </si>
   <si>
@@ -228,33 +228,36 @@
     <t>Pallets</t>
   </si>
   <si>
+    <t>Cantidad de pallets</t>
+  </si>
+  <si>
+    <t>39*20*18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realicé el calculo para 52 semanas </t>
+  </si>
+  <si>
     <t>Camión</t>
   </si>
   <si>
-    <t>Cantidad de pallets</t>
-  </si>
-  <si>
     <t>USD 60000</t>
   </si>
   <si>
-    <t>39*20*18</t>
-  </si>
-  <si>
     <t>Combustible anual</t>
   </si>
   <si>
     <t>8000 Litros</t>
   </si>
   <si>
-    <t xml:space="preserve">Realicé el calculo para 52 semanas </t>
-  </si>
-  <si>
     <t>Mantenimiento anual</t>
   </si>
   <si>
     <t>Seguro anual</t>
   </si>
   <si>
+    <t>Cantidad de pallets x semana</t>
+  </si>
+  <si>
     <t>Patente anual</t>
   </si>
   <si>
@@ -286,9 +289,6 @@
   </si>
   <si>
     <t>Flete recolección + última milla</t>
-  </si>
-  <si>
-    <t>Cantidad de pallets x semana</t>
   </si>
   <si>
     <t>TOTAL SEMANAL</t>
@@ -480,68 +480,86 @@
     </xf>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -552,26 +570,8 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -1010,736 +1010,736 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
+      <c r="A1" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
     </row>
     <row r="2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
     </row>
     <row r="3" ht="23.25" customHeight="1">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="K3" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="24" t="s">
+      <c r="L3" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="N3" s="24" t="s">
+      <c r="N3" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="O3" s="27" t="s">
+      <c r="O3" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="P3" s="27" t="s">
-        <v>91</v>
+      <c r="P3" s="22" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="31">
+      <c r="A4" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="24">
         <v>53.0</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="24">
         <f t="shared" ref="C4:C14" si="1">B4/52</f>
         <v>1.019230769</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="24">
         <f t="shared" ref="D4:D14" si="2">C4*1000000</f>
         <v>1019230.769</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="24">
         <v>150.0</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="24">
         <f t="shared" ref="F4:F14" si="3">ROUND(D4/E4,0)</f>
         <v>6795</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="28">
         <v>12.0</v>
       </c>
-      <c r="H4" s="34">
+      <c r="H4" s="30">
         <f t="shared" ref="H4:H14" si="4">ROUND(F4/G4,0)</f>
         <v>566</v>
       </c>
-      <c r="I4" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J4" s="34">
+      <c r="I4" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="30">
         <f t="shared" ref="J4:J14" si="5">3*5</f>
         <v>15</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="28">
         <v>8.0</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="28">
         <v>2.9</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="30">
         <f t="shared" ref="M4:M14" si="6">L4*N4</f>
         <v>348</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="30">
         <f t="shared" ref="N4:N14" si="7">J4*K4</f>
         <v>120</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="32">
         <f t="shared" ref="O4:O14" si="8">H4/N4</f>
         <v>4.716666667</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="33">
         <f t="shared" ref="P4:P14" si="9">IF(O4&lt;1,1,ROUND(O4,0))</f>
         <v>5</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="31">
+      <c r="A5" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="24">
         <v>7.0</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="24">
         <f t="shared" si="1"/>
         <v>0.1346153846</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="24">
         <f t="shared" si="2"/>
         <v>134615.3846</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="24">
         <v>150.0</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="24">
         <f t="shared" si="3"/>
         <v>897</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="28">
         <v>12.0</v>
       </c>
-      <c r="H5" s="34">
+      <c r="H5" s="30">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="I5" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" s="34">
+      <c r="I5" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" s="30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K5" s="33">
+      <c r="K5" s="28">
         <v>8.0</v>
       </c>
-      <c r="L5" s="33">
+      <c r="L5" s="28">
         <v>2.9</v>
       </c>
-      <c r="M5" s="34">
+      <c r="M5" s="30">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="30">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O5" s="36">
+      <c r="O5" s="32">
         <f t="shared" si="8"/>
         <v>0.625</v>
       </c>
-      <c r="P5" s="37">
+      <c r="P5" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="31">
+      <c r="A6" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="24">
         <v>16.0</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="24">
         <f t="shared" si="1"/>
         <v>0.3076923077</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="24">
         <f t="shared" si="2"/>
         <v>307692.3077</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="24">
         <v>150.0</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="24">
         <f t="shared" si="3"/>
         <v>2051</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="28">
         <v>12.0</v>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="30">
         <f t="shared" si="4"/>
         <v>171</v>
       </c>
-      <c r="I6" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J6" s="34">
+      <c r="I6" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K6" s="33">
+      <c r="K6" s="28">
         <v>8.0</v>
       </c>
-      <c r="L6" s="33">
+      <c r="L6" s="28">
         <v>2.9</v>
       </c>
-      <c r="M6" s="34">
+      <c r="M6" s="30">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="30">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O6" s="36">
+      <c r="O6" s="32">
         <f t="shared" si="8"/>
         <v>1.425</v>
       </c>
-      <c r="P6" s="37">
+      <c r="P6" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="31">
+      <c r="A7" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="24">
         <v>49.0</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="24">
         <f t="shared" si="1"/>
         <v>0.9423076923</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="24">
         <f t="shared" si="2"/>
         <v>942307.6923</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="24">
         <v>150.0</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="24">
         <f t="shared" si="3"/>
         <v>6282</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="28">
         <v>12.0</v>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="30">
         <f t="shared" si="4"/>
         <v>524</v>
       </c>
-      <c r="I7" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="34">
+      <c r="I7" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J7" s="30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K7" s="28">
         <v>8.0</v>
       </c>
-      <c r="L7" s="33">
+      <c r="L7" s="28">
         <v>2.9</v>
       </c>
-      <c r="M7" s="34">
+      <c r="M7" s="30">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N7" s="34">
+      <c r="N7" s="30">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O7" s="36">
+      <c r="O7" s="32">
         <f t="shared" si="8"/>
         <v>4.366666667</v>
       </c>
-      <c r="P7" s="37">
+      <c r="P7" s="33">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="31">
+      <c r="A8" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="24">
         <v>7.0</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="24">
         <f t="shared" si="1"/>
         <v>0.1346153846</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="24">
         <f t="shared" si="2"/>
         <v>134615.3846</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="24">
         <v>150.0</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="24">
         <f t="shared" si="3"/>
         <v>897</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="28">
         <v>12.0</v>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="30">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="I8" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J8" s="34">
+      <c r="I8" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K8" s="33">
+      <c r="K8" s="28">
         <v>8.0</v>
       </c>
-      <c r="L8" s="33">
+      <c r="L8" s="28">
         <v>2.9</v>
       </c>
-      <c r="M8" s="34">
+      <c r="M8" s="30">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N8" s="34">
+      <c r="N8" s="30">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O8" s="36">
+      <c r="O8" s="32">
         <f t="shared" si="8"/>
         <v>0.625</v>
       </c>
-      <c r="P8" s="37">
+      <c r="P8" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="31">
+      <c r="A9" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="24">
         <v>16.0</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="24">
         <f t="shared" si="1"/>
         <v>0.3076923077</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="24">
         <f t="shared" si="2"/>
         <v>307692.3077</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="24">
         <v>150.0</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="24">
         <f t="shared" si="3"/>
         <v>2051</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="28">
         <v>12.0</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="30">
         <f t="shared" si="4"/>
         <v>171</v>
       </c>
-      <c r="I9" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9" s="34">
+      <c r="I9" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" s="30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K9" s="33">
+      <c r="K9" s="28">
         <v>8.0</v>
       </c>
-      <c r="L9" s="33">
+      <c r="L9" s="28">
         <v>2.9</v>
       </c>
-      <c r="M9" s="34">
+      <c r="M9" s="30">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N9" s="34">
+      <c r="N9" s="30">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O9" s="36">
+      <c r="O9" s="32">
         <f t="shared" si="8"/>
         <v>1.425</v>
       </c>
-      <c r="P9" s="37">
+      <c r="P9" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="31">
+      <c r="A10" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="24">
         <v>12.0</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="24">
         <f t="shared" si="1"/>
         <v>0.2307692308</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="24">
         <f t="shared" si="2"/>
         <v>230769.2308</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="24">
         <v>150.0</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="24">
         <f t="shared" si="3"/>
         <v>1538</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="28">
         <v>12.0</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="30">
         <f t="shared" si="4"/>
         <v>128</v>
       </c>
-      <c r="I10" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J10" s="34">
+      <c r="I10" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" s="30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K10" s="33">
+      <c r="K10" s="28">
         <v>8.0</v>
       </c>
-      <c r="L10" s="33">
+      <c r="L10" s="28">
         <v>2.9</v>
       </c>
-      <c r="M10" s="34">
+      <c r="M10" s="30">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N10" s="34">
+      <c r="N10" s="30">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O10" s="36">
+      <c r="O10" s="32">
         <f t="shared" si="8"/>
         <v>1.066666667</v>
       </c>
-      <c r="P10" s="37">
+      <c r="P10" s="33">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="31">
+      <c r="A11" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="24">
         <v>28.0</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="24">
         <f t="shared" si="1"/>
         <v>0.5384615385</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="24">
         <f t="shared" si="2"/>
         <v>538461.5385</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="24">
         <v>150.0</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="24">
         <f t="shared" si="3"/>
         <v>3590</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="28">
         <v>12.0</v>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="30">
         <f t="shared" si="4"/>
         <v>299</v>
       </c>
-      <c r="I11" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J11" s="34">
+      <c r="I11" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" s="30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K11" s="33">
+      <c r="K11" s="28">
         <v>8.0</v>
       </c>
-      <c r="L11" s="33">
+      <c r="L11" s="28">
         <v>2.9</v>
       </c>
-      <c r="M11" s="34">
+      <c r="M11" s="30">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N11" s="34">
+      <c r="N11" s="30">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O11" s="36">
+      <c r="O11" s="32">
         <f t="shared" si="8"/>
         <v>2.491666667</v>
       </c>
-      <c r="P11" s="37">
+      <c r="P11" s="33">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="24">
         <v>61.0</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="24">
         <f t="shared" si="1"/>
         <v>1.173076923</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="24">
         <f t="shared" si="2"/>
         <v>1173076.923</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="24">
         <v>150.0</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="24">
         <f t="shared" si="3"/>
         <v>7821</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="28">
         <v>12.0</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="30">
         <f t="shared" si="4"/>
         <v>652</v>
       </c>
-      <c r="I12" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J12" s="34">
+      <c r="I12" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K12" s="33">
+      <c r="K12" s="28">
         <v>8.0</v>
       </c>
-      <c r="L12" s="33">
+      <c r="L12" s="28">
         <v>2.9</v>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="30">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N12" s="34">
+      <c r="N12" s="30">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O12" s="36">
+      <c r="O12" s="32">
         <f t="shared" si="8"/>
         <v>5.433333333</v>
       </c>
-      <c r="P12" s="37">
+      <c r="P12" s="33">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="24">
         <v>74.0</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="24">
         <f t="shared" si="1"/>
         <v>1.423076923</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="24">
         <f t="shared" si="2"/>
         <v>1423076.923</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="24">
         <v>150.0</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="24">
         <f t="shared" si="3"/>
         <v>9487</v>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="28">
         <v>12.0</v>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="30">
         <f t="shared" si="4"/>
         <v>791</v>
       </c>
-      <c r="I13" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13" s="34">
+      <c r="I13" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" s="30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K13" s="33">
+      <c r="K13" s="28">
         <v>8.0</v>
       </c>
-      <c r="L13" s="33">
+      <c r="L13" s="28">
         <v>2.9</v>
       </c>
-      <c r="M13" s="34">
+      <c r="M13" s="30">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N13" s="34">
+      <c r="N13" s="30">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O13" s="36">
+      <c r="O13" s="32">
         <f t="shared" si="8"/>
         <v>6.591666667</v>
       </c>
-      <c r="P13" s="37">
+      <c r="P13" s="33">
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="24">
         <v>32.0</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="24">
         <f t="shared" si="1"/>
         <v>0.6153846154</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="24">
         <f t="shared" si="2"/>
         <v>615384.6154</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="24">
         <v>150.0</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="24">
         <f t="shared" si="3"/>
         <v>4103</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="28">
         <v>12.0</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="30">
         <f t="shared" si="4"/>
         <v>342</v>
       </c>
-      <c r="I14" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J14" s="34">
+      <c r="I14" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J14" s="30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K14" s="33">
+      <c r="K14" s="28">
         <v>8.0</v>
       </c>
-      <c r="L14" s="33">
+      <c r="L14" s="28">
         <v>2.9</v>
       </c>
-      <c r="M14" s="34">
+      <c r="M14" s="30">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N14" s="34">
+      <c r="N14" s="30">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O14" s="36">
+      <c r="O14" s="32">
         <f t="shared" si="8"/>
         <v>2.85</v>
       </c>
-      <c r="P14" s="37">
+      <c r="P14" s="33">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -1768,734 +1768,734 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
       <c r="K16" s="43"/>
-      <c r="L16" s="20"/>
+      <c r="L16" s="17"/>
       <c r="M16" s="43"/>
-      <c r="N16" s="20"/>
+      <c r="N16" s="17"/>
       <c r="O16" s="43"/>
     </row>
     <row r="17">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="24" t="s">
+      <c r="H18" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="I18" s="24" t="s">
+      <c r="I18" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="J18" s="24" t="s">
+      <c r="J18" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="K18" s="24" t="s">
+      <c r="K18" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="L18" s="24" t="s">
+      <c r="L18" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="M18" s="24" t="s">
+      <c r="M18" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="N18" s="24" t="s">
+      <c r="N18" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="O18" s="27" t="s">
+      <c r="O18" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="P18" s="27" t="s">
-        <v>91</v>
+      <c r="P18" s="22" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="31">
+      <c r="A19" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24">
         <v>101.0</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="24">
         <f t="shared" ref="C19:C29" si="10">B19/52</f>
         <v>1.942307692</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="24">
         <f t="shared" ref="D19:D29" si="11">C19*1000000</f>
         <v>1942307.692</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="24">
         <v>150.0</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="24">
         <f t="shared" ref="F19:F29" si="12">ROUND(D19/E19,0)</f>
         <v>12949</v>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="28">
         <v>12.0</v>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="30">
         <f t="shared" ref="H19:H29" si="13">ROUND(F19/G19,0)</f>
         <v>1079</v>
       </c>
-      <c r="I19" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J19" s="34">
+      <c r="I19" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J19" s="30">
         <f t="shared" ref="J19:J29" si="14">3*5</f>
         <v>15</v>
       </c>
-      <c r="K19" s="33">
+      <c r="K19" s="28">
         <v>8.0</v>
       </c>
-      <c r="L19" s="33">
+      <c r="L19" s="28">
         <v>2.9</v>
       </c>
-      <c r="M19" s="34">
+      <c r="M19" s="30">
         <f t="shared" ref="M19:M29" si="15">L19*N19</f>
         <v>348</v>
       </c>
-      <c r="N19" s="34">
+      <c r="N19" s="30">
         <f t="shared" ref="N19:N29" si="16">J19*K19</f>
         <v>120</v>
       </c>
-      <c r="O19" s="36">
+      <c r="O19" s="32">
         <f t="shared" ref="O19:O29" si="17">H19/N19</f>
         <v>8.991666667</v>
       </c>
-      <c r="P19" s="37">
+      <c r="P19" s="33">
         <f t="shared" ref="P19:P29" si="18">IF(O19&lt;1,1,ROUND(O19,0))</f>
         <v>9</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="31">
+      <c r="A20" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="24">
         <v>13.0</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="24">
         <f t="shared" si="10"/>
         <v>0.25</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="24">
         <f t="shared" si="11"/>
         <v>250000</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="24">
         <v>150.0</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="24">
         <f t="shared" si="12"/>
         <v>1667</v>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="28">
         <v>12.0</v>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="30">
         <f t="shared" si="13"/>
         <v>139</v>
       </c>
-      <c r="I20" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J20" s="34">
+      <c r="I20" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J20" s="30">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K20" s="33">
+      <c r="K20" s="28">
         <v>8.0</v>
       </c>
-      <c r="L20" s="33">
+      <c r="L20" s="28">
         <v>2.9</v>
       </c>
-      <c r="M20" s="34">
+      <c r="M20" s="30">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N20" s="34">
+      <c r="N20" s="30">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O20" s="36">
+      <c r="O20" s="32">
         <f t="shared" si="17"/>
         <v>1.158333333</v>
       </c>
-      <c r="P20" s="37">
+      <c r="P20" s="33">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="31">
+      <c r="A21" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="24">
         <v>31.0</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="24">
         <f t="shared" si="10"/>
         <v>0.5961538462</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="24">
         <f t="shared" si="11"/>
         <v>596153.8462</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="24">
         <v>150.0</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="24">
         <f t="shared" si="12"/>
         <v>3974</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="28">
         <v>12.0</v>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="30">
         <f t="shared" si="13"/>
         <v>331</v>
       </c>
-      <c r="I21" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J21" s="34">
+      <c r="I21" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J21" s="30">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K21" s="33">
+      <c r="K21" s="28">
         <v>8.0</v>
       </c>
-      <c r="L21" s="33">
+      <c r="L21" s="28">
         <v>2.9</v>
       </c>
-      <c r="M21" s="34">
+      <c r="M21" s="30">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N21" s="34">
+      <c r="N21" s="30">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O21" s="36">
+      <c r="O21" s="32">
         <f t="shared" si="17"/>
         <v>2.758333333</v>
       </c>
-      <c r="P21" s="37">
+      <c r="P21" s="33">
         <f t="shared" si="18"/>
         <v>3</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="A22" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="24">
         <v>94.0</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="24">
         <f t="shared" si="10"/>
         <v>1.807692308</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="24">
         <f t="shared" si="11"/>
         <v>1807692.308</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="24">
         <v>150.0</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="24">
         <f t="shared" si="12"/>
         <v>12051</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="28">
         <v>12.0</v>
       </c>
-      <c r="H22" s="34">
+      <c r="H22" s="30">
         <f t="shared" si="13"/>
         <v>1004</v>
       </c>
-      <c r="I22" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J22" s="34">
+      <c r="I22" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="30">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K22" s="33">
+      <c r="K22" s="28">
         <v>8.0</v>
       </c>
-      <c r="L22" s="33">
+      <c r="L22" s="28">
         <v>2.9</v>
       </c>
-      <c r="M22" s="34">
+      <c r="M22" s="30">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N22" s="34">
+      <c r="N22" s="30">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O22" s="36">
+      <c r="O22" s="32">
         <f t="shared" si="17"/>
         <v>8.366666667</v>
       </c>
-      <c r="P22" s="37">
+      <c r="P22" s="33">
         <f t="shared" si="18"/>
         <v>8</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="31">
+      <c r="A23" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="24">
         <v>13.0</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="24">
         <f t="shared" si="10"/>
         <v>0.25</v>
       </c>
-      <c r="D23" s="31">
+      <c r="D23" s="24">
         <f t="shared" si="11"/>
         <v>250000</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E23" s="24">
         <v>150.0</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="24">
         <f t="shared" si="12"/>
         <v>1667</v>
       </c>
-      <c r="G23" s="33">
+      <c r="G23" s="28">
         <v>12.0</v>
       </c>
-      <c r="H23" s="34">
+      <c r="H23" s="30">
         <f t="shared" si="13"/>
         <v>139</v>
       </c>
-      <c r="I23" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J23" s="34">
+      <c r="I23" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J23" s="30">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K23" s="33">
+      <c r="K23" s="28">
         <v>8.0</v>
       </c>
-      <c r="L23" s="33">
+      <c r="L23" s="28">
         <v>2.9</v>
       </c>
-      <c r="M23" s="34">
+      <c r="M23" s="30">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N23" s="34">
+      <c r="N23" s="30">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O23" s="36">
+      <c r="O23" s="32">
         <f t="shared" si="17"/>
         <v>1.158333333</v>
       </c>
-      <c r="P23" s="37">
+      <c r="P23" s="33">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="A24" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="24">
         <v>31.0</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="24">
         <f t="shared" si="10"/>
         <v>0.5961538462</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="24">
         <f t="shared" si="11"/>
         <v>596153.8462</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="24">
         <v>150.0</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="24">
         <f t="shared" si="12"/>
         <v>3974</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="28">
         <v>12.0</v>
       </c>
-      <c r="H24" s="34">
+      <c r="H24" s="30">
         <f t="shared" si="13"/>
         <v>331</v>
       </c>
-      <c r="I24" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J24" s="34">
+      <c r="I24" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J24" s="30">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K24" s="33">
+      <c r="K24" s="28">
         <v>8.0</v>
       </c>
-      <c r="L24" s="33">
+      <c r="L24" s="28">
         <v>2.9</v>
       </c>
-      <c r="M24" s="34">
+      <c r="M24" s="30">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N24" s="34">
+      <c r="N24" s="30">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O24" s="36">
+      <c r="O24" s="32">
         <f t="shared" si="17"/>
         <v>2.758333333</v>
       </c>
-      <c r="P24" s="37">
+      <c r="P24" s="33">
         <f t="shared" si="18"/>
         <v>3</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="31">
+      <c r="A25" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="24">
         <v>23.0</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="24">
         <f t="shared" si="10"/>
         <v>0.4423076923</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="24">
         <f t="shared" si="11"/>
         <v>442307.6923</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="24">
         <v>150.0</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="24">
         <f t="shared" si="12"/>
         <v>2949</v>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="28">
         <v>12.0</v>
       </c>
-      <c r="H25" s="34">
+      <c r="H25" s="30">
         <f t="shared" si="13"/>
         <v>246</v>
       </c>
-      <c r="I25" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J25" s="34">
+      <c r="I25" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J25" s="30">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K25" s="33">
+      <c r="K25" s="28">
         <v>8.0</v>
       </c>
-      <c r="L25" s="33">
+      <c r="L25" s="28">
         <v>2.9</v>
       </c>
-      <c r="M25" s="34">
+      <c r="M25" s="30">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N25" s="34">
+      <c r="N25" s="30">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O25" s="36">
+      <c r="O25" s="32">
         <f t="shared" si="17"/>
         <v>2.05</v>
       </c>
-      <c r="P25" s="37">
+      <c r="P25" s="33">
         <f t="shared" si="18"/>
         <v>2</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="31">
+      <c r="A26" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="24">
         <v>53.0</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="24">
         <f t="shared" si="10"/>
         <v>1.019230769</v>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="24">
         <f t="shared" si="11"/>
         <v>1019230.769</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="24">
         <v>150.0</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="24">
         <f t="shared" si="12"/>
         <v>6795</v>
       </c>
-      <c r="G26" s="33">
+      <c r="G26" s="28">
         <v>12.0</v>
       </c>
-      <c r="H26" s="34">
+      <c r="H26" s="30">
         <f t="shared" si="13"/>
         <v>566</v>
       </c>
-      <c r="I26" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J26" s="34">
+      <c r="I26" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J26" s="30">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K26" s="33">
+      <c r="K26" s="28">
         <v>8.0</v>
       </c>
-      <c r="L26" s="33">
+      <c r="L26" s="28">
         <v>2.9</v>
       </c>
-      <c r="M26" s="34">
+      <c r="M26" s="30">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N26" s="34">
+      <c r="N26" s="30">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O26" s="36">
+      <c r="O26" s="32">
         <f t="shared" si="17"/>
         <v>4.716666667</v>
       </c>
-      <c r="P26" s="37">
+      <c r="P26" s="33">
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="24">
         <v>118.0</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="24">
         <f t="shared" si="10"/>
         <v>2.269230769</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="24">
         <f t="shared" si="11"/>
         <v>2269230.769</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="24">
         <v>150.0</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="24">
         <f t="shared" si="12"/>
         <v>15128</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="28">
         <v>12.0</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="30">
         <f t="shared" si="13"/>
         <v>1261</v>
       </c>
-      <c r="I27" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J27" s="34">
+      <c r="I27" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J27" s="30">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="28">
         <v>8.0</v>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="28">
         <v>2.9</v>
       </c>
-      <c r="M27" s="34">
+      <c r="M27" s="30">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="30">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O27" s="36">
+      <c r="O27" s="32">
         <f t="shared" si="17"/>
         <v>10.50833333</v>
       </c>
-      <c r="P27" s="37">
+      <c r="P27" s="33">
         <f t="shared" si="18"/>
         <v>11</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="24">
         <v>141.0</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="24">
         <f t="shared" si="10"/>
         <v>2.711538462</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="24">
         <f t="shared" si="11"/>
         <v>2711538.462</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="24">
         <v>150.0</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="24">
         <f t="shared" si="12"/>
         <v>18077</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="28">
         <v>12.0</v>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="30">
         <f t="shared" si="13"/>
         <v>1506</v>
       </c>
-      <c r="I28" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J28" s="34">
+      <c r="I28" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J28" s="30">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="28">
         <v>8.0</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="28">
         <v>2.9</v>
       </c>
-      <c r="M28" s="34">
+      <c r="M28" s="30">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N28" s="34">
+      <c r="N28" s="30">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O28" s="36">
+      <c r="O28" s="32">
         <f t="shared" si="17"/>
         <v>12.55</v>
       </c>
-      <c r="P28" s="37">
+      <c r="P28" s="33">
         <f t="shared" si="18"/>
         <v>13</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="24">
         <v>61.0</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="24">
         <f t="shared" si="10"/>
         <v>1.173076923</v>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="24">
         <f t="shared" si="11"/>
         <v>1173076.923</v>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="24">
         <v>150.0</v>
       </c>
-      <c r="F29" s="31">
+      <c r="F29" s="24">
         <f t="shared" si="12"/>
         <v>7821</v>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="28">
         <v>12.0</v>
       </c>
-      <c r="H29" s="34">
+      <c r="H29" s="30">
         <f t="shared" si="13"/>
         <v>652</v>
       </c>
-      <c r="I29" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="J29" s="34">
+      <c r="I29" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J29" s="30">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K29" s="33">
+      <c r="K29" s="28">
         <v>8.0</v>
       </c>
-      <c r="L29" s="33">
+      <c r="L29" s="28">
         <v>2.9</v>
       </c>
-      <c r="M29" s="34">
+      <c r="M29" s="30">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N29" s="34">
+      <c r="N29" s="30">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O29" s="36">
+      <c r="O29" s="32">
         <f t="shared" si="17"/>
         <v>5.433333333</v>
       </c>
-      <c r="P29" s="37">
+      <c r="P29" s="33">
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
@@ -2524,20 +2524,20 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
       <c r="K31" s="43"/>
-      <c r="L31" s="20"/>
+      <c r="L31" s="17"/>
       <c r="M31" s="43"/>
-      <c r="N31" s="20"/>
+      <c r="N31" s="17"/>
       <c r="O31" s="43"/>
     </row>
     <row r="32">
@@ -2547,20 +2547,20 @@
       <c r="C32" s="3"/>
       <c r="D32" s="4"/>
       <c r="F32" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="4"/>
       <c r="L32" s="45"/>
     </row>
     <row r="33">
-      <c r="B33" s="6" t="s">
-        <v>87</v>
+      <c r="B33" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="4"/>
-      <c r="F33" s="6" t="s">
-        <v>87</v>
+      <c r="F33" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="4"/>
@@ -2568,43 +2568,43 @@
     </row>
     <row r="34">
       <c r="B34" s="46" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C34" s="46" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D34" s="46" t="s">
-        <v>37</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G34" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="H34" s="13" t="s">
-        <v>37</v>
+      <c r="H34" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="L34" s="45"/>
     </row>
     <row r="35">
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="27" t="s">
         <v>94</v>
       </c>
       <c r="C35" s="47" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D35" s="47">
         <f>60000*1400</f>
         <v>84000000</v>
       </c>
-      <c r="F35" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="G35" s="13">
+      <c r="F35" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G35" s="18">
         <v>220.0</v>
       </c>
-      <c r="H35" s="13">
+      <c r="H35" s="18">
         <v>300000.0</v>
       </c>
       <c r="L35" s="48" t="s">
@@ -2615,18 +2615,18 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="25" t="s">
-        <v>75</v>
+      <c r="B36" s="27" t="s">
+        <v>76</v>
       </c>
       <c r="C36" s="46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D36" s="47">
         <v>1.82E7</v>
       </c>
-      <c r="F36" s="28"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="30"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="36"/>
       <c r="I36" s="49"/>
       <c r="J36" s="49"/>
       <c r="L36" s="50" t="s">
@@ -2637,7 +2637,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="27" t="s">
         <v>78</v>
       </c>
       <c r="C37" s="46">
@@ -2646,11 +2646,11 @@
       <c r="D37" s="47">
         <v>6000000.0</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="G37" s="13"/>
-      <c r="H37" s="32">
+      <c r="G37" s="18"/>
+      <c r="H37" s="37">
         <f>G35*H35</f>
         <v>66000000</v>
       </c>
@@ -2664,7 +2664,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="27" t="s">
         <v>79</v>
       </c>
       <c r="C38" s="53">
@@ -2686,8 +2686,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="25" t="s">
-        <v>80</v>
+      <c r="B39" s="27" t="s">
+        <v>81</v>
       </c>
       <c r="C39" s="53">
         <v>0.04</v>
@@ -2723,11 +2723,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="25" t="s">
-        <v>83</v>
+      <c r="B41" s="27" t="s">
+        <v>84</v>
       </c>
       <c r="C41" s="46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D41" s="47">
         <v>2000000.0</v>
@@ -2744,11 +2744,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="25" t="s">
+      <c r="B42" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="46" t="s">
         <v>85</v>
-      </c>
-      <c r="C42" s="46" t="s">
-        <v>84</v>
       </c>
       <c r="D42" s="47">
         <v>2200000.0</v>
@@ -2777,11 +2777,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="25" t="s">
+      <c r="B44" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C44" s="25"/>
-      <c r="D44" s="26">
+      <c r="C44" s="27"/>
+      <c r="D44" s="29">
         <f>SUM(D35:D42)</f>
         <v>119960000</v>
       </c>
@@ -2900,13 +2900,13 @@
         <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1">
         <v>150.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1">
         <v>53.0</v>
@@ -2935,22 +2935,22 @@
       <c r="M3" s="1">
         <v>94.0</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="5">
         <v>101.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1">
         <v>150.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1">
         <v>7.0</v>
@@ -2985,16 +2985,16 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1">
         <v>150.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1">
         <v>16.0</v>
@@ -3029,16 +3029,16 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1">
         <v>150.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1">
         <v>49.0</v>
@@ -3073,16 +3073,16 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1">
         <v>150.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1">
         <v>7.0</v>
@@ -3117,16 +3117,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1">
         <v>150.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1">
         <v>16.0</v>
@@ -3161,16 +3161,16 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1">
         <v>150.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1">
         <v>12.0</v>
@@ -3205,16 +3205,16 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C10" s="1">
         <v>150.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1">
         <v>28.0</v>
@@ -3284,10 +3284,10 @@
       <c r="L11" s="1">
         <v>103.0</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="5">
         <v>110.0</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="5">
         <v>118.0</v>
       </c>
     </row>
@@ -3307,31 +3307,31 @@
       <c r="E12" s="1">
         <v>74.0</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <v>84.0</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="5">
         <v>89.0</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="5">
         <v>95.0</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="5">
         <v>100.0</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="5">
         <v>107.0</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="5">
         <v>115.0</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="5">
         <v>123.0</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="5">
         <v>132.0</v>
       </c>
-      <c r="N12" s="7">
+      <c r="N12" s="5">
         <v>141.0</v>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
         <v>180.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1">
         <v>32.0</v>
@@ -3383,131 +3383,131 @@
       <c r="B14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <v>353.0</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <v>403.0</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="5">
         <v>428.0</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="5">
         <v>453.0</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="5">
         <v>481.0</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="5">
         <v>515.0</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="5">
         <v>552.0</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="5">
         <v>591.0</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="5">
         <v>633.0</v>
       </c>
-      <c r="N14" s="7">
+      <c r="N14" s="5">
         <v>679.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="M17" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="N17" s="11" t="s">
+      <c r="N17" s="10" t="s">
         <v>69</v>
       </c>
       <c r="O17" s="12" t="s">
         <v>70</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="14">
+        <v>16</v>
+      </c>
+      <c r="B18" s="13">
         <v>48.0</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13">
         <v>0.9230769230769231</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="13">
         <v>923076.9230769231</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="14">
         <v>150.0</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="14">
         <v>455000.0</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="14">
         <v>12.0</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <v>37917.0</v>
       </c>
-      <c r="I18" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J18" s="14">
+      <c r="I18" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J18" s="13">
         <v>15.0</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="14">
         <v>8.0</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="14">
         <v>2.9</v>
       </c>
-      <c r="M18" s="14">
+      <c r="M18" s="13">
         <v>348.0</v>
       </c>
-      <c r="N18" s="14">
+      <c r="N18" s="13">
         <v>120.0</v>
       </c>
-      <c r="O18" s="19">
+      <c r="O18" s="16">
         <v>315.975</v>
       </c>
       <c r="P18" s="12">
@@ -3516,48 +3516,48 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="14">
+        <v>20</v>
+      </c>
+      <c r="B19" s="13">
         <v>8.0</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="13">
         <v>0.15384615384615385</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="13">
         <v>153846.15384615384</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="14">
         <v>150.0</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="14">
         <v>83000.0</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="14">
         <v>12.0</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <v>6917.0</v>
       </c>
-      <c r="I19" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J19" s="14">
+      <c r="I19" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J19" s="13">
         <v>15.0</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="14">
         <v>8.0</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="14">
         <v>2.9</v>
       </c>
-      <c r="M19" s="14">
+      <c r="M19" s="13">
         <v>348.0</v>
       </c>
-      <c r="N19" s="14">
+      <c r="N19" s="13">
         <v>120.0</v>
       </c>
-      <c r="O19" s="19">
+      <c r="O19" s="16">
         <v>57.641666666666666</v>
       </c>
       <c r="P19" s="12">
@@ -3566,48 +3566,48 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="14">
+        <v>23</v>
+      </c>
+      <c r="B20" s="13">
         <v>19.0</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13">
         <v>0.36538461538461536</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13">
         <v>365384.6153846154</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="14">
         <v>150.0</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="14">
         <v>188000.0</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="14">
         <v>12.0</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <v>15667.0</v>
       </c>
-      <c r="I20" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J20" s="14">
+      <c r="I20" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J20" s="13">
         <v>15.0</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="14">
         <v>8.0</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="14">
         <v>2.9</v>
       </c>
-      <c r="M20" s="14">
+      <c r="M20" s="13">
         <v>348.0</v>
       </c>
-      <c r="N20" s="14">
+      <c r="N20" s="13">
         <v>120.0</v>
       </c>
-      <c r="O20" s="19">
+      <c r="O20" s="16">
         <v>130.55833333333334</v>
       </c>
       <c r="P20" s="12">
@@ -3616,48 +3616,48 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="14">
+        <v>26</v>
+      </c>
+      <c r="B21" s="13">
         <v>78.0</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="13">
         <v>1.5</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="13">
         <v>1500000.0</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="14">
         <v>150.0</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="14">
         <v>737000.0</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="14">
         <v>12.0</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <v>61417.0</v>
       </c>
-      <c r="I21" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J21" s="14">
+      <c r="I21" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J21" s="13">
         <v>15.0</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="14">
         <v>8.0</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="14">
         <v>2.9</v>
       </c>
-      <c r="M21" s="14">
+      <c r="M21" s="13">
         <v>348.0</v>
       </c>
-      <c r="N21" s="14">
+      <c r="N21" s="13">
         <v>120.0</v>
       </c>
-      <c r="O21" s="19">
+      <c r="O21" s="16">
         <v>511.80833333333334</v>
       </c>
       <c r="P21" s="12">
@@ -3666,48 +3666,48 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="14">
+        <v>29</v>
+      </c>
+      <c r="B22" s="13">
         <v>5.0</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13">
         <v>0.09615384615384616</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13">
         <v>96153.84615384616</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="14">
         <v>150.0</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="14">
         <v>48000.0</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="14">
         <v>12.0</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="13">
         <v>4000.0</v>
       </c>
-      <c r="I22" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J22" s="14">
+      <c r="I22" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="13">
         <v>15.0</v>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="14">
         <v>8.0</v>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="14">
         <v>2.9</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="13">
         <v>348.0</v>
       </c>
-      <c r="N22" s="14">
+      <c r="N22" s="13">
         <v>120.0</v>
       </c>
-      <c r="O22" s="19">
+      <c r="O22" s="16">
         <v>33.333333333333336</v>
       </c>
       <c r="P22" s="12">
@@ -3716,48 +3716,48 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="14">
+        <v>31</v>
+      </c>
+      <c r="B23" s="13">
         <v>11.0</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13">
         <v>0.21153846153846154</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="13">
         <v>211538.46153846153</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="14">
         <v>150.0</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="14">
         <v>107000.0</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="14">
         <v>12.0</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="13">
         <v>8917.0</v>
       </c>
-      <c r="I23" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J23" s="14">
+      <c r="I23" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J23" s="13">
         <v>15.0</v>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="14">
         <v>8.0</v>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="14">
         <v>2.9</v>
       </c>
-      <c r="M23" s="14">
+      <c r="M23" s="13">
         <v>348.0</v>
       </c>
-      <c r="N23" s="14">
+      <c r="N23" s="13">
         <v>120.0</v>
       </c>
-      <c r="O23" s="19">
+      <c r="O23" s="16">
         <v>74.30833333333334</v>
       </c>
       <c r="P23" s="12">
@@ -3766,48 +3766,48 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="14">
+        <v>37</v>
+      </c>
+      <c r="B24" s="13">
         <v>16.0</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="13">
         <v>0.3076923076923077</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="13">
         <v>307692.3076923077</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="14">
         <v>150.0</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="14">
         <v>154000.0</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="14">
         <v>12.0</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="13">
         <v>12833.0</v>
       </c>
-      <c r="I24" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J24" s="14">
+      <c r="I24" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J24" s="13">
         <v>15.0</v>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="14">
         <v>8.0</v>
       </c>
-      <c r="L24" s="16">
+      <c r="L24" s="14">
         <v>2.9</v>
       </c>
-      <c r="M24" s="14">
+      <c r="M24" s="13">
         <v>348.0</v>
       </c>
-      <c r="N24" s="14">
+      <c r="N24" s="13">
         <v>120.0</v>
       </c>
-      <c r="O24" s="19">
+      <c r="O24" s="16">
         <v>106.94166666666666</v>
       </c>
       <c r="P24" s="12">
@@ -3816,48 +3816,48 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="14">
+        <v>46</v>
+      </c>
+      <c r="B25" s="13">
         <v>37.0</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="13">
         <v>0.7115384615384616</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="13">
         <v>711538.4615384616</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="14">
         <v>150.0</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="14">
         <v>353000.0</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="14">
         <v>12.0</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="13">
         <v>29417.0</v>
       </c>
-      <c r="I25" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J25" s="14">
+      <c r="I25" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J25" s="13">
         <v>15.0</v>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="14">
         <v>8.0</v>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="14">
         <v>2.9</v>
       </c>
-      <c r="M25" s="14">
+      <c r="M25" s="13">
         <v>348.0</v>
       </c>
-      <c r="N25" s="14">
+      <c r="N25" s="13">
         <v>120.0</v>
       </c>
-      <c r="O25" s="19">
+      <c r="O25" s="16">
         <v>245.14166666666668</v>
       </c>
       <c r="P25" s="12">
@@ -3868,46 +3868,46 @@
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="13">
         <v>75.0</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="13">
         <v>1.4423076923076923</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="13">
         <v>1442307.6923076923</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="14">
         <v>150.0</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="14">
         <v>269000.0</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="14">
         <v>12.0</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="13">
         <v>22417.0</v>
       </c>
-      <c r="I26" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J26" s="14">
+      <c r="I26" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J26" s="13">
         <v>15.0</v>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="14">
         <v>8.0</v>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="14">
         <v>2.9</v>
       </c>
-      <c r="M26" s="14">
+      <c r="M26" s="13">
         <v>348.0</v>
       </c>
-      <c r="N26" s="14">
+      <c r="N26" s="13">
         <v>120.0</v>
       </c>
-      <c r="O26" s="19">
+      <c r="O26" s="16">
         <v>186.80833333333334</v>
       </c>
       <c r="P26" s="12">
@@ -3918,46 +3918,46 @@
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="13">
         <v>71.0</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13">
         <v>1.3653846153846154</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13">
         <v>1365384.6153846155</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="14">
         <v>150.0</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="14">
         <v>562000.0</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="14">
         <v>12.0</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <v>46833.0</v>
       </c>
-      <c r="I27" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J27" s="14">
+      <c r="I27" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J27" s="13">
         <v>15.0</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="14">
         <v>8.0</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="14">
         <v>2.9</v>
       </c>
-      <c r="M27" s="14">
+      <c r="M27" s="13">
         <v>348.0</v>
       </c>
-      <c r="N27" s="14">
+      <c r="N27" s="13">
         <v>120.0</v>
       </c>
-      <c r="O27" s="19">
+      <c r="O27" s="16">
         <v>390.275</v>
       </c>
       <c r="P27" s="12">
@@ -3968,46 +3968,46 @@
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="13">
         <v>18.0</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13">
         <v>0.34615384615384615</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13">
         <v>346153.8461538461</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="14">
         <v>150.0</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="14">
         <v>145000.0</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="14">
         <v>12.0</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <v>12083.0</v>
       </c>
-      <c r="I28" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J28" s="14">
+      <c r="I28" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J28" s="13">
         <v>15.0</v>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="14">
         <v>8.0</v>
       </c>
-      <c r="L28" s="16">
+      <c r="L28" s="14">
         <v>2.9</v>
       </c>
-      <c r="M28" s="14">
+      <c r="M28" s="13">
         <v>348.0</v>
       </c>
-      <c r="N28" s="14">
+      <c r="N28" s="13">
         <v>120.0</v>
       </c>
-      <c r="O28" s="19">
+      <c r="O28" s="16">
         <v>100.69166666666666</v>
       </c>
       <c r="P28" s="12">
@@ -4037,395 +4037,395 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="4"/>
-      <c r="F2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>16</v>
+      <c r="F2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="6" t="s">
-        <v>19</v>
+      <c r="B3" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="4"/>
       <c r="F3" s="8" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="9" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="10">
+        <v>48</v>
+      </c>
+      <c r="F4" s="11">
         <f>SUM(D5:D13)</f>
         <v>131700000</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="11">
         <f>SUM(D6:D13)+SUM(D6:D13)*30%</f>
         <v>54210000</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="11">
         <f t="shared" ref="H4:J4" si="1">G4+G4*30%</f>
         <v>70473000</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="11">
         <f t="shared" si="1"/>
         <v>91614900</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="11">
         <f t="shared" si="1"/>
         <v>119099370</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="11">
         <f>J4+J4*30%+(D5+D5*25%)</f>
         <v>267329181</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="11">
         <f>K4-(D5+D5*25%)</f>
         <v>154829181</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="11">
         <f t="shared" ref="M4:O4" si="2">L4+L4*30%</f>
         <v>201277935.3</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="11">
         <f t="shared" si="2"/>
         <v>261661315.9</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="11">
         <f t="shared" si="2"/>
         <v>340159710.7</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="B5" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="19">
         <f>60000*1500</f>
         <v>90000000</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="18" t="s">
+      <c r="B6" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="15">
+      <c r="C6" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="19">
         <v>1.92E7</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="11">
         <f>ROUND(SUM(F4:O4),0)</f>
         <v>1692354594</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="21">
         <v>3.0</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="19">
         <f>C7*1800000</f>
         <v>5400000</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="23">
         <v>0.05</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="25">
         <f>D5*C8</f>
         <v>4500000</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="21">
+      <c r="B9" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="23">
         <v>0.04</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="25">
         <f>D5*C9</f>
         <v>3600000</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="22">
+      <c r="B10" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="26"/>
+      <c r="D10" s="25">
         <v>1800000.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="23"/>
-      <c r="D11" s="22">
+      <c r="B11" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="26"/>
+      <c r="D11" s="25">
         <v>3000000.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="18" t="s">
+      <c r="B12" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="15">
+      <c r="C12" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="19">
         <v>2000000.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" s="15">
+      <c r="D13" s="19">
         <v>2200000.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="26">
+      <c r="C15" s="27"/>
+      <c r="D15" s="29">
         <f>SUM(D5:D13)</f>
         <v>131700000</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
-      <c r="F18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>16</v>
+      <c r="F18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="s">
-        <v>87</v>
+      <c r="B19" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="4"/>
       <c r="F19" s="8" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="13" t="s">
+      <c r="B20" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" s="10">
+      <c r="C20" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="11">
         <f>D23</f>
         <v>53750000</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="11">
         <f>F20+F20*10%</f>
         <v>59125000</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="11">
         <f t="shared" ref="H20:O20" si="3">G20+G20*15%</f>
         <v>67993750</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="11">
         <f t="shared" si="3"/>
         <v>78192812.5</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="11">
         <f t="shared" si="3"/>
         <v>89921734.38</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="11">
         <f t="shared" si="3"/>
         <v>103409994.5</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="11">
         <f t="shared" si="3"/>
         <v>118921493.7</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="11">
         <f t="shared" si="3"/>
         <v>136759717.8</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="11">
         <f t="shared" si="3"/>
         <v>157273675.4</v>
       </c>
-      <c r="O20" s="10">
+      <c r="O20" s="11">
         <f t="shared" si="3"/>
         <v>180864726.7</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="13">
+      <c r="B21" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="18">
         <v>215.0</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="18">
         <v>250000.0</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="30"/>
-      <c r="F22" s="5" t="s">
+      <c r="B22" s="34"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="36"/>
+      <c r="F22" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="11">
         <f>SUM(F20:O20)</f>
         <v>1046212905</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="32">
+      <c r="C23" s="18"/>
+      <c r="D23" s="37">
         <f>C21*D21</f>
         <v>53750000</v>
       </c>

--- a/2026/Proyecto_Final/drive_proyecto_final/Técnico/Logistica de distribución.xlsx
+++ b/2026/Proyecto_Final/drive_proyecto_final/Técnico/Logistica de distribución.xlsx
@@ -81,6 +81,9 @@
     <t>Free</t>
   </si>
   <si>
+    <t>CHASIS 8 PALLETS</t>
+  </si>
+  <si>
     <t>A03</t>
   </si>
   <si>
@@ -90,13 +93,49 @@
     <t>Clásicas</t>
   </si>
   <si>
+    <t>AÑO 1</t>
+  </si>
+  <si>
+    <t>AÑO 2</t>
+  </si>
+  <si>
+    <t>AÑO 3</t>
+  </si>
+  <si>
+    <t>AÑO 4</t>
+  </si>
+  <si>
+    <t>AÑO 5</t>
+  </si>
+  <si>
     <t>A04</t>
   </si>
   <si>
+    <t>AÑO 6</t>
+  </si>
+  <si>
     <t>Pepas chocolate y batata 150gr.</t>
   </si>
   <si>
-    <t>CHASIS 8 PALLETS</t>
+    <t>AÑO 7</t>
+  </si>
+  <si>
+    <t>AÑO 8</t>
+  </si>
+  <si>
+    <t>AÑO 9</t>
+  </si>
+  <si>
+    <t>AÑO 10</t>
+  </si>
+  <si>
+    <t>Costos</t>
+  </si>
+  <si>
+    <t>Datos</t>
+  </si>
+  <si>
+    <t>Monto en pesos</t>
   </si>
   <si>
     <t>A05</t>
@@ -111,57 +150,18 @@
     <t>Bizcochos sabor queso 150gr.</t>
   </si>
   <si>
-    <t>AÑO 1</t>
-  </si>
-  <si>
-    <t>AÑO 2</t>
-  </si>
-  <si>
-    <t>AÑO 3</t>
-  </si>
-  <si>
     <t>A07</t>
   </si>
   <si>
-    <t>AÑO 4</t>
-  </si>
-  <si>
     <t>Polvorones free 150gr.</t>
   </si>
   <si>
-    <t>AÑO 5</t>
-  </si>
-  <si>
-    <t>AÑO 6</t>
-  </si>
-  <si>
-    <t>AÑO 7</t>
-  </si>
-  <si>
-    <t>AÑO 8</t>
-  </si>
-  <si>
-    <t>AÑO 9</t>
-  </si>
-  <si>
-    <t>AÑO 10</t>
-  </si>
-  <si>
-    <t>Costos</t>
-  </si>
-  <si>
     <t>A08</t>
   </si>
   <si>
     <t>Polvorones 150gr.</t>
   </si>
   <si>
-    <t>Datos</t>
-  </si>
-  <si>
-    <t>Monto en pesos</t>
-  </si>
-  <si>
     <t>B01</t>
   </si>
   <si>
@@ -255,31 +255,31 @@
     <t>Seguro anual</t>
   </si>
   <si>
+    <t>Patente anual</t>
+  </si>
+  <si>
+    <t>Rastreo satelital</t>
+  </si>
+  <si>
+    <t>Peajes</t>
+  </si>
+  <si>
+    <t>Sueldo Chofer</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Sueldo Planifcador de ruta</t>
+  </si>
+  <si>
+    <t>LOGÍSTICA TERCIARIZADA</t>
+  </si>
+  <si>
+    <t>CHASIS</t>
+  </si>
+  <si>
     <t>Cantidad de pallets x semana</t>
-  </si>
-  <si>
-    <t>Patente anual</t>
-  </si>
-  <si>
-    <t>Rastreo satelital</t>
-  </si>
-  <si>
-    <t>Peajes</t>
-  </si>
-  <si>
-    <t>Sueldo Chofer</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Sueldo Planifcador de ruta</t>
-  </si>
-  <si>
-    <t>LOGÍSTICA TERCIARIZADA</t>
-  </si>
-  <si>
-    <t>CHASIS</t>
   </si>
   <si>
     <t>Costo</t>
@@ -480,12 +480,12 @@
     </xf>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -495,11 +495,11 @@
     <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
@@ -519,36 +519,48 @@
     <xf borderId="4" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
@@ -560,18 +572,6 @@
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -1046,700 +1046,700 @@
       <c r="O2" s="17"/>
     </row>
     <row r="3" ht="23.25" customHeight="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="20" t="s">
+      <c r="L3" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="M3" s="20" t="s">
+      <c r="M3" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="N3" s="20" t="s">
+      <c r="N3" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="O3" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="P3" s="22" t="s">
-        <v>80</v>
+      <c r="P3" s="27" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="28">
         <v>53.0</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="28">
         <f t="shared" ref="C4:C14" si="1">B4/52</f>
         <v>1.019230769</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="28">
         <f t="shared" ref="D4:D14" si="2">C4*1000000</f>
         <v>1019230.769</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="28">
         <v>150.0</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="28">
         <f t="shared" ref="F4:F14" si="3">ROUND(D4/E4,0)</f>
         <v>6795</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="33">
         <v>12.0</v>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="34">
         <f t="shared" ref="H4:H14" si="4">ROUND(F4/G4,0)</f>
         <v>566</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="I4" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="34">
         <f t="shared" ref="J4:J14" si="5">3*5</f>
         <v>15</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="33">
         <v>8.0</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="33">
         <v>2.9</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="34">
         <f t="shared" ref="M4:M14" si="6">L4*N4</f>
         <v>348</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="34">
         <f t="shared" ref="N4:N14" si="7">J4*K4</f>
         <v>120</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="36">
         <f t="shared" ref="O4:O14" si="8">H4/N4</f>
         <v>4.716666667</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="37">
         <f t="shared" ref="P4:P14" si="9">IF(O4&lt;1,1,ROUND(O4,0))</f>
         <v>5</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="28">
         <v>7.0</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="28">
         <f t="shared" si="1"/>
         <v>0.1346153846</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="28">
         <f t="shared" si="2"/>
         <v>134615.3846</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="28">
         <v>150.0</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="28">
         <f t="shared" si="3"/>
         <v>897</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="33">
         <v>12.0</v>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="34">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="I5" s="31" t="s">
+      <c r="I5" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="34">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K5" s="28">
+      <c r="K5" s="33">
         <v>8.0</v>
       </c>
-      <c r="L5" s="28">
+      <c r="L5" s="33">
         <v>2.9</v>
       </c>
-      <c r="M5" s="30">
+      <c r="M5" s="34">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N5" s="30">
+      <c r="N5" s="34">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O5" s="32">
+      <c r="O5" s="36">
         <f t="shared" si="8"/>
         <v>0.625</v>
       </c>
-      <c r="P5" s="33">
+      <c r="P5" s="37">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="24">
+      <c r="A6" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="28">
         <v>16.0</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="28">
         <f t="shared" si="1"/>
         <v>0.3076923077</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="28">
         <f t="shared" si="2"/>
         <v>307692.3077</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="28">
         <v>150.0</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="28">
         <f t="shared" si="3"/>
         <v>2051</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="33">
         <v>12.0</v>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="34">
         <f t="shared" si="4"/>
         <v>171</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="I6" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="30">
+      <c r="J6" s="34">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K6" s="28">
+      <c r="K6" s="33">
         <v>8.0</v>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="33">
         <v>2.9</v>
       </c>
-      <c r="M6" s="30">
+      <c r="M6" s="34">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N6" s="30">
+      <c r="N6" s="34">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O6" s="32">
+      <c r="O6" s="36">
         <f t="shared" si="8"/>
         <v>1.425</v>
       </c>
-      <c r="P6" s="33">
+      <c r="P6" s="37">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="24">
+      <c r="A7" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="28">
         <v>49.0</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="28">
         <f t="shared" si="1"/>
         <v>0.9423076923</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="28">
         <f t="shared" si="2"/>
         <v>942307.6923</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="28">
         <v>150.0</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="28">
         <f t="shared" si="3"/>
         <v>6282</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="33">
         <v>12.0</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="34">
         <f t="shared" si="4"/>
         <v>524</v>
       </c>
-      <c r="I7" s="31" t="s">
+      <c r="I7" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="34">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K7" s="28">
+      <c r="K7" s="33">
         <v>8.0</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="33">
         <v>2.9</v>
       </c>
-      <c r="M7" s="30">
+      <c r="M7" s="34">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N7" s="30">
+      <c r="N7" s="34">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O7" s="32">
+      <c r="O7" s="36">
         <f t="shared" si="8"/>
         <v>4.366666667</v>
       </c>
-      <c r="P7" s="33">
+      <c r="P7" s="37">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="24">
+      <c r="A8" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="28">
         <v>7.0</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="28">
         <f t="shared" si="1"/>
         <v>0.1346153846</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="28">
         <f t="shared" si="2"/>
         <v>134615.3846</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="28">
         <v>150.0</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="28">
         <f t="shared" si="3"/>
         <v>897</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="33">
         <v>12.0</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="34">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="34">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="33">
         <v>8.0</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="33">
         <v>2.9</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="34">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="34">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O8" s="32">
+      <c r="O8" s="36">
         <f t="shared" si="8"/>
         <v>0.625</v>
       </c>
-      <c r="P8" s="33">
+      <c r="P8" s="37">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="24">
+      <c r="A9" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="28">
         <v>16.0</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="28">
         <f t="shared" si="1"/>
         <v>0.3076923077</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="28">
         <f t="shared" si="2"/>
         <v>307692.3077</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="28">
         <v>150.0</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="28">
         <f t="shared" si="3"/>
         <v>2051</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="33">
         <v>12.0</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="34">
         <f t="shared" si="4"/>
         <v>171</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="34">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K9" s="28">
+      <c r="K9" s="33">
         <v>8.0</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="33">
         <v>2.9</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="34">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N9" s="30">
+      <c r="N9" s="34">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O9" s="32">
+      <c r="O9" s="36">
         <f t="shared" si="8"/>
         <v>1.425</v>
       </c>
-      <c r="P9" s="33">
+      <c r="P9" s="37">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="24">
+      <c r="A10" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="28">
         <v>12.0</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="28">
         <f t="shared" si="1"/>
         <v>0.2307692308</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="28">
         <f t="shared" si="2"/>
         <v>230769.2308</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="28">
         <v>150.0</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="28">
         <f t="shared" si="3"/>
         <v>1538</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="33">
         <v>12.0</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="34">
         <f t="shared" si="4"/>
         <v>128</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10" s="34">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="33">
         <v>8.0</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="33">
         <v>2.9</v>
       </c>
-      <c r="M10" s="30">
+      <c r="M10" s="34">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N10" s="30">
+      <c r="N10" s="34">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O10" s="32">
+      <c r="O10" s="36">
         <f t="shared" si="8"/>
         <v>1.066666667</v>
       </c>
-      <c r="P10" s="33">
+      <c r="P10" s="37">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="24">
+      <c r="A11" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="28">
         <v>28.0</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="28">
         <f t="shared" si="1"/>
         <v>0.5384615385</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="28">
         <f t="shared" si="2"/>
         <v>538461.5385</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="28">
         <v>150.0</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="28">
         <f t="shared" si="3"/>
         <v>3590</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="33">
         <v>12.0</v>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="34">
         <f t="shared" si="4"/>
         <v>299</v>
       </c>
-      <c r="I11" s="31" t="s">
+      <c r="I11" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="34">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K11" s="28">
+      <c r="K11" s="33">
         <v>8.0</v>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="33">
         <v>2.9</v>
       </c>
-      <c r="M11" s="30">
+      <c r="M11" s="34">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N11" s="30">
+      <c r="N11" s="34">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O11" s="32">
+      <c r="O11" s="36">
         <f t="shared" si="8"/>
         <v>2.491666667</v>
       </c>
-      <c r="P11" s="33">
+      <c r="P11" s="37">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="28">
         <v>61.0</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="28">
         <f t="shared" si="1"/>
         <v>1.173076923</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="28">
         <f t="shared" si="2"/>
         <v>1173076.923</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="28">
         <v>150.0</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="28">
         <f t="shared" si="3"/>
         <v>7821</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="33">
         <v>12.0</v>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="34">
         <f t="shared" si="4"/>
         <v>652</v>
       </c>
-      <c r="I12" s="31" t="s">
+      <c r="I12" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J12" s="30">
+      <c r="J12" s="34">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="33">
         <v>8.0</v>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="33">
         <v>2.9</v>
       </c>
-      <c r="M12" s="30">
+      <c r="M12" s="34">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N12" s="30">
+      <c r="N12" s="34">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O12" s="32">
+      <c r="O12" s="36">
         <f t="shared" si="8"/>
         <v>5.433333333</v>
       </c>
-      <c r="P12" s="33">
+      <c r="P12" s="37">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="28">
         <v>74.0</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="28">
         <f t="shared" si="1"/>
         <v>1.423076923</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="28">
         <f t="shared" si="2"/>
         <v>1423076.923</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="28">
         <v>150.0</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="28">
         <f t="shared" si="3"/>
         <v>9487</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="33">
         <v>12.0</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="34">
         <f t="shared" si="4"/>
         <v>791</v>
       </c>
-      <c r="I13" s="31" t="s">
+      <c r="I13" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J13" s="30">
+      <c r="J13" s="34">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="33">
         <v>8.0</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="33">
         <v>2.9</v>
       </c>
-      <c r="M13" s="30">
+      <c r="M13" s="34">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N13" s="30">
+      <c r="N13" s="34">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O13" s="32">
+      <c r="O13" s="36">
         <f t="shared" si="8"/>
         <v>6.591666667</v>
       </c>
-      <c r="P13" s="33">
+      <c r="P13" s="37">
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="28">
         <v>32.0</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="28">
         <f t="shared" si="1"/>
         <v>0.6153846154</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="28">
         <f t="shared" si="2"/>
         <v>615384.6154</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="28">
         <v>150.0</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="28">
         <f t="shared" si="3"/>
         <v>4103</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="33">
         <v>12.0</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="34">
         <f t="shared" si="4"/>
         <v>342</v>
       </c>
-      <c r="I14" s="31" t="s">
+      <c r="I14" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="30">
+      <c r="J14" s="34">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="K14" s="28">
+      <c r="K14" s="33">
         <v>8.0</v>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="33">
         <v>2.9</v>
       </c>
-      <c r="M14" s="30">
+      <c r="M14" s="34">
         <f t="shared" si="6"/>
         <v>348</v>
       </c>
-      <c r="N14" s="30">
+      <c r="N14" s="34">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="O14" s="32">
+      <c r="O14" s="36">
         <f t="shared" si="8"/>
         <v>2.85</v>
       </c>
-      <c r="P14" s="33">
+      <c r="P14" s="37">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -1802,700 +1802,700 @@
       <c r="O17" s="17"/>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="G18" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="H18" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="I18" s="20" t="s">
+      <c r="I18" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J18" s="20" t="s">
+      <c r="J18" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="K18" s="20" t="s">
+      <c r="K18" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="L18" s="20" t="s">
+      <c r="L18" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="M18" s="20" t="s">
+      <c r="M18" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="N18" s="20" t="s">
+      <c r="N18" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="O18" s="22" t="s">
+      <c r="O18" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="P18" s="22" t="s">
-        <v>80</v>
+      <c r="P18" s="27" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="28">
         <v>101.0</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="28">
         <f t="shared" ref="C19:C29" si="10">B19/52</f>
         <v>1.942307692</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="28">
         <f t="shared" ref="D19:D29" si="11">C19*1000000</f>
         <v>1942307.692</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="28">
         <v>150.0</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="28">
         <f t="shared" ref="F19:F29" si="12">ROUND(D19/E19,0)</f>
         <v>12949</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="33">
         <v>12.0</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="34">
         <f t="shared" ref="H19:H29" si="13">ROUND(F19/G19,0)</f>
         <v>1079</v>
       </c>
-      <c r="I19" s="31" t="s">
+      <c r="I19" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J19" s="30">
+      <c r="J19" s="34">
         <f t="shared" ref="J19:J29" si="14">3*5</f>
         <v>15</v>
       </c>
-      <c r="K19" s="28">
+      <c r="K19" s="33">
         <v>8.0</v>
       </c>
-      <c r="L19" s="28">
+      <c r="L19" s="33">
         <v>2.9</v>
       </c>
-      <c r="M19" s="30">
+      <c r="M19" s="34">
         <f t="shared" ref="M19:M29" si="15">L19*N19</f>
         <v>348</v>
       </c>
-      <c r="N19" s="30">
+      <c r="N19" s="34">
         <f t="shared" ref="N19:N29" si="16">J19*K19</f>
         <v>120</v>
       </c>
-      <c r="O19" s="32">
+      <c r="O19" s="36">
         <f t="shared" ref="O19:O29" si="17">H19/N19</f>
         <v>8.991666667</v>
       </c>
-      <c r="P19" s="33">
+      <c r="P19" s="37">
         <f t="shared" ref="P19:P29" si="18">IF(O19&lt;1,1,ROUND(O19,0))</f>
         <v>9</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="28">
         <v>13.0</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="28">
         <f t="shared" si="10"/>
         <v>0.25</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="28">
         <f t="shared" si="11"/>
         <v>250000</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="28">
         <v>150.0</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="28">
         <f t="shared" si="12"/>
         <v>1667</v>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="33">
         <v>12.0</v>
       </c>
-      <c r="H20" s="30">
+      <c r="H20" s="34">
         <f t="shared" si="13"/>
         <v>139</v>
       </c>
-      <c r="I20" s="31" t="s">
+      <c r="I20" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J20" s="30">
+      <c r="J20" s="34">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="33">
         <v>8.0</v>
       </c>
-      <c r="L20" s="28">
+      <c r="L20" s="33">
         <v>2.9</v>
       </c>
-      <c r="M20" s="30">
+      <c r="M20" s="34">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N20" s="30">
+      <c r="N20" s="34">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O20" s="32">
+      <c r="O20" s="36">
         <f t="shared" si="17"/>
         <v>1.158333333</v>
       </c>
-      <c r="P20" s="33">
+      <c r="P20" s="37">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="24">
+      <c r="A21" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="28">
         <v>31.0</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="28">
         <f t="shared" si="10"/>
         <v>0.5961538462</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="28">
         <f t="shared" si="11"/>
         <v>596153.8462</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="28">
         <v>150.0</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="28">
         <f t="shared" si="12"/>
         <v>3974</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="33">
         <v>12.0</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="34">
         <f t="shared" si="13"/>
         <v>331</v>
       </c>
-      <c r="I21" s="31" t="s">
+      <c r="I21" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="34">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="33">
         <v>8.0</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="33">
         <v>2.9</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="34">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N21" s="30">
+      <c r="N21" s="34">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="36">
         <f t="shared" si="17"/>
         <v>2.758333333</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="37">
         <f t="shared" si="18"/>
         <v>3</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="24">
+      <c r="A22" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="28">
         <v>94.0</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="28">
         <f t="shared" si="10"/>
         <v>1.807692308</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="28">
         <f t="shared" si="11"/>
         <v>1807692.308</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="28">
         <v>150.0</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="28">
         <f t="shared" si="12"/>
         <v>12051</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="33">
         <v>12.0</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="34">
         <f t="shared" si="13"/>
         <v>1004</v>
       </c>
-      <c r="I22" s="31" t="s">
+      <c r="I22" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="34">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K22" s="28">
+      <c r="K22" s="33">
         <v>8.0</v>
       </c>
-      <c r="L22" s="28">
+      <c r="L22" s="33">
         <v>2.9</v>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="34">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N22" s="30">
+      <c r="N22" s="34">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="36">
         <f t="shared" si="17"/>
         <v>8.366666667</v>
       </c>
-      <c r="P22" s="33">
+      <c r="P22" s="37">
         <f t="shared" si="18"/>
         <v>8</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="24">
+      <c r="A23" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="28">
         <v>13.0</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="28">
         <f t="shared" si="10"/>
         <v>0.25</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="28">
         <f t="shared" si="11"/>
         <v>250000</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="28">
         <v>150.0</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="28">
         <f t="shared" si="12"/>
         <v>1667</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="33">
         <v>12.0</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H23" s="34">
         <f t="shared" si="13"/>
         <v>139</v>
       </c>
-      <c r="I23" s="31" t="s">
+      <c r="I23" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J23" s="30">
+      <c r="J23" s="34">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="33">
         <v>8.0</v>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="33">
         <v>2.9</v>
       </c>
-      <c r="M23" s="30">
+      <c r="M23" s="34">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N23" s="30">
+      <c r="N23" s="34">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O23" s="32">
+      <c r="O23" s="36">
         <f t="shared" si="17"/>
         <v>1.158333333</v>
       </c>
-      <c r="P23" s="33">
+      <c r="P23" s="37">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="24">
+      <c r="A24" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="28">
         <v>31.0</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="28">
         <f t="shared" si="10"/>
         <v>0.5961538462</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="28">
         <f t="shared" si="11"/>
         <v>596153.8462</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="28">
         <v>150.0</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="28">
         <f t="shared" si="12"/>
         <v>3974</v>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="33">
         <v>12.0</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="34">
         <f t="shared" si="13"/>
         <v>331</v>
       </c>
-      <c r="I24" s="31" t="s">
+      <c r="I24" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="34">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K24" s="28">
+      <c r="K24" s="33">
         <v>8.0</v>
       </c>
-      <c r="L24" s="28">
+      <c r="L24" s="33">
         <v>2.9</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="34">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N24" s="30">
+      <c r="N24" s="34">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="36">
         <f t="shared" si="17"/>
         <v>2.758333333</v>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="37">
         <f t="shared" si="18"/>
         <v>3</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="24">
+      <c r="A25" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="28">
         <v>23.0</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="28">
         <f t="shared" si="10"/>
         <v>0.4423076923</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="28">
         <f t="shared" si="11"/>
         <v>442307.6923</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="28">
         <v>150.0</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="28">
         <f t="shared" si="12"/>
         <v>2949</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="33">
         <v>12.0</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="34">
         <f t="shared" si="13"/>
         <v>246</v>
       </c>
-      <c r="I25" s="31" t="s">
+      <c r="I25" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="34">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K25" s="28">
+      <c r="K25" s="33">
         <v>8.0</v>
       </c>
-      <c r="L25" s="28">
+      <c r="L25" s="33">
         <v>2.9</v>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="34">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N25" s="30">
+      <c r="N25" s="34">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="36">
         <f t="shared" si="17"/>
         <v>2.05</v>
       </c>
-      <c r="P25" s="33">
+      <c r="P25" s="37">
         <f t="shared" si="18"/>
         <v>2</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="24">
+      <c r="A26" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="28">
         <v>53.0</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="28">
         <f t="shared" si="10"/>
         <v>1.019230769</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="28">
         <f t="shared" si="11"/>
         <v>1019230.769</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="28">
         <v>150.0</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="28">
         <f t="shared" si="12"/>
         <v>6795</v>
       </c>
-      <c r="G26" s="28">
+      <c r="G26" s="33">
         <v>12.0</v>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="34">
         <f t="shared" si="13"/>
         <v>566</v>
       </c>
-      <c r="I26" s="31" t="s">
+      <c r="I26" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J26" s="30">
+      <c r="J26" s="34">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K26" s="28">
+      <c r="K26" s="33">
         <v>8.0</v>
       </c>
-      <c r="L26" s="28">
+      <c r="L26" s="33">
         <v>2.9</v>
       </c>
-      <c r="M26" s="30">
+      <c r="M26" s="34">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N26" s="30">
+      <c r="N26" s="34">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O26" s="32">
+      <c r="O26" s="36">
         <f t="shared" si="17"/>
         <v>4.716666667</v>
       </c>
-      <c r="P26" s="33">
+      <c r="P26" s="37">
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="28">
         <v>118.0</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="28">
         <f t="shared" si="10"/>
         <v>2.269230769</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="28">
         <f t="shared" si="11"/>
         <v>2269230.769</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="28">
         <v>150.0</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="28">
         <f t="shared" si="12"/>
         <v>15128</v>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="33">
         <v>12.0</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="34">
         <f t="shared" si="13"/>
         <v>1261</v>
       </c>
-      <c r="I27" s="31" t="s">
+      <c r="I27" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="34">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K27" s="28">
+      <c r="K27" s="33">
         <v>8.0</v>
       </c>
-      <c r="L27" s="28">
+      <c r="L27" s="33">
         <v>2.9</v>
       </c>
-      <c r="M27" s="30">
+      <c r="M27" s="34">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N27" s="30">
+      <c r="N27" s="34">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="36">
         <f t="shared" si="17"/>
         <v>10.50833333</v>
       </c>
-      <c r="P27" s="33">
+      <c r="P27" s="37">
         <f t="shared" si="18"/>
         <v>11</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="28">
         <v>141.0</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="28">
         <f t="shared" si="10"/>
         <v>2.711538462</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="28">
         <f t="shared" si="11"/>
         <v>2711538.462</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="28">
         <v>150.0</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="28">
         <f t="shared" si="12"/>
         <v>18077</v>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="33">
         <v>12.0</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="34">
         <f t="shared" si="13"/>
         <v>1506</v>
       </c>
-      <c r="I28" s="31" t="s">
+      <c r="I28" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="34">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K28" s="28">
+      <c r="K28" s="33">
         <v>8.0</v>
       </c>
-      <c r="L28" s="28">
+      <c r="L28" s="33">
         <v>2.9</v>
       </c>
-      <c r="M28" s="30">
+      <c r="M28" s="34">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N28" s="30">
+      <c r="N28" s="34">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="36">
         <f t="shared" si="17"/>
         <v>12.55</v>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="37">
         <f t="shared" si="18"/>
         <v>13</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="28">
         <v>61.0</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="28">
         <f t="shared" si="10"/>
         <v>1.173076923</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="28">
         <f t="shared" si="11"/>
         <v>1173076.923</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="28">
         <v>150.0</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="28">
         <f t="shared" si="12"/>
         <v>7821</v>
       </c>
-      <c r="G29" s="28">
+      <c r="G29" s="33">
         <v>12.0</v>
       </c>
-      <c r="H29" s="30">
+      <c r="H29" s="34">
         <f t="shared" si="13"/>
         <v>652</v>
       </c>
-      <c r="I29" s="31" t="s">
+      <c r="I29" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J29" s="30">
+      <c r="J29" s="34">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="K29" s="28">
+      <c r="K29" s="33">
         <v>8.0</v>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="33">
         <v>2.9</v>
       </c>
-      <c r="M29" s="30">
+      <c r="M29" s="34">
         <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N29" s="30">
+      <c r="N29" s="34">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="O29" s="32">
+      <c r="O29" s="36">
         <f t="shared" si="17"/>
         <v>5.433333333</v>
       </c>
-      <c r="P29" s="33">
+      <c r="P29" s="37">
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
@@ -2547,7 +2547,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="4"/>
       <c r="F32" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="4"/>
@@ -2555,12 +2555,12 @@
     </row>
     <row r="33">
       <c r="B33" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="4"/>
       <c r="F33" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="4"/>
@@ -2568,13 +2568,13 @@
     </row>
     <row r="34">
       <c r="B34" s="46" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C34" s="46" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D34" s="46" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>89</v>
@@ -2583,12 +2583,12 @@
         <v>93</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L34" s="45"/>
     </row>
     <row r="35">
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="25" t="s">
         <v>94</v>
       </c>
       <c r="C35" s="47" t="s">
@@ -2615,18 +2615,18 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="25" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D36" s="47">
         <v>1.82E7</v>
       </c>
-      <c r="F36" s="34"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="36"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="31"/>
       <c r="I36" s="49"/>
       <c r="J36" s="49"/>
       <c r="L36" s="50" t="s">
@@ -2637,7 +2637,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="25" t="s">
         <v>78</v>
       </c>
       <c r="C37" s="46">
@@ -2650,7 +2650,7 @@
         <v>56</v>
       </c>
       <c r="G37" s="18"/>
-      <c r="H37" s="37">
+      <c r="H37" s="32">
         <f>G35*H35</f>
         <v>66000000</v>
       </c>
@@ -2664,7 +2664,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="25" t="s">
         <v>79</v>
       </c>
       <c r="C38" s="53">
@@ -2686,8 +2686,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="27" t="s">
-        <v>81</v>
+      <c r="B39" s="25" t="s">
+        <v>80</v>
       </c>
       <c r="C39" s="53">
         <v>0.04</v>
@@ -2723,11 +2723,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="46" t="s">
         <v>84</v>
-      </c>
-      <c r="C41" s="46" t="s">
-        <v>85</v>
       </c>
       <c r="D41" s="47">
         <v>2000000.0</v>
@@ -2744,11 +2744,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="27" t="s">
-        <v>86</v>
+      <c r="B42" s="25" t="s">
+        <v>85</v>
       </c>
       <c r="C42" s="46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D42" s="47">
         <v>2200000.0</v>
@@ -2777,11 +2777,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="C44" s="27"/>
-      <c r="D44" s="29">
+      <c r="C44" s="25"/>
+      <c r="D44" s="26">
         <f>SUM(D35:D42)</f>
         <v>119960000</v>
       </c>
@@ -2935,7 +2935,7 @@
       <c r="M3" s="1">
         <v>94.0</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="6">
         <v>101.0</v>
       </c>
     </row>
@@ -2985,16 +2985,16 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1">
         <v>150.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1">
         <v>16.0</v>
@@ -3029,10 +3029,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C6" s="1">
         <v>150.0</v>
@@ -3073,10 +3073,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1">
         <v>150.0</v>
@@ -3117,16 +3117,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1">
         <v>150.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1">
         <v>16.0</v>
@@ -3161,10 +3161,10 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1">
         <v>150.0</v>
@@ -3205,16 +3205,16 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" s="1">
         <v>150.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" s="1">
         <v>28.0</v>
@@ -3284,10 +3284,10 @@
       <c r="L11" s="1">
         <v>103.0</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="6">
         <v>110.0</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="6">
         <v>118.0</v>
       </c>
     </row>
@@ -3307,31 +3307,31 @@
       <c r="E12" s="1">
         <v>74.0</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="6">
         <v>84.0</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="6">
         <v>89.0</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="6">
         <v>95.0</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="6">
         <v>100.0</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="6">
         <v>107.0</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="6">
         <v>115.0</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="6">
         <v>123.0</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="6">
         <v>132.0</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" s="6">
         <v>141.0</v>
       </c>
     </row>
@@ -3383,78 +3383,78 @@
       <c r="B14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="6">
         <v>353.0</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="6">
         <v>403.0</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="6">
         <v>428.0</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="6">
         <v>453.0</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="6">
         <v>481.0</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="6">
         <v>515.0</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="6">
         <v>552.0</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14" s="6">
         <v>591.0</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="6">
         <v>633.0</v>
       </c>
-      <c r="N14" s="5">
+      <c r="N14" s="6">
         <v>679.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="L17" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="M17" s="10" t="s">
+      <c r="M17" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="N17" s="10" t="s">
+      <c r="N17" s="11" t="s">
         <v>69</v>
       </c>
       <c r="O17" s="12" t="s">
@@ -3566,7 +3566,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="13">
         <v>19.0</v>
@@ -3616,7 +3616,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B21" s="13">
         <v>78.0</v>
@@ -3666,7 +3666,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B22" s="13">
         <v>5.0</v>
@@ -3716,7 +3716,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B23" s="13">
         <v>11.0</v>
@@ -3766,7 +3766,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B24" s="13">
         <v>16.0</v>
@@ -3816,7 +3816,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B25" s="13">
         <v>37.0</v>
@@ -4037,121 +4037,121 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="4"/>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="4"/>
       <c r="F3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="M3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>42</v>
-      </c>
       <c r="O3" s="8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="11">
+        <v>40</v>
+      </c>
+      <c r="F4" s="10">
         <f>SUM(D5:D13)</f>
         <v>131700000</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <f>SUM(D6:D13)+SUM(D6:D13)*30%</f>
         <v>54210000</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="10">
         <f t="shared" ref="H4:J4" si="1">G4+G4*30%</f>
         <v>70473000</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="10">
         <f t="shared" si="1"/>
         <v>91614900</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="10">
         <f t="shared" si="1"/>
         <v>119099370</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="10">
         <f>J4+J4*30%+(D5+D5*25%)</f>
         <v>267329181</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="10">
         <f>K4-(D5+D5*25%)</f>
         <v>154829181</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="10">
         <f t="shared" ref="M4:O4" si="2">L4+L4*30%</f>
         <v>201277935.3</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="10">
         <f t="shared" si="2"/>
         <v>261661315.9</v>
       </c>
-      <c r="O4" s="11">
+      <c r="O4" s="10">
         <f t="shared" si="2"/>
         <v>340159710.7</v>
       </c>
@@ -4172,16 +4172,16 @@
       <c r="B6" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>77</v>
       </c>
       <c r="D6" s="19">
         <v>1.92E7</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <f>ROUND(SUM(F4:O4),0)</f>
         <v>1692354594</v>
       </c>
@@ -4190,7 +4190,7 @@
       <c r="B7" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="20">
         <v>3.0</v>
       </c>
       <c r="D7" s="19">
@@ -4202,50 +4202,50 @@
       <c r="B8" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="22">
         <v>0.05</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="23">
         <f>D5*C8</f>
         <v>4500000</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="23">
+        <v>80</v>
+      </c>
+      <c r="C9" s="22">
         <v>0.04</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="23">
         <f>D5*C9</f>
         <v>3600000</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="25">
+        <v>81</v>
+      </c>
+      <c r="C10" s="24"/>
+      <c r="D10" s="23">
         <v>1800000.0</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="25">
+        <v>82</v>
+      </c>
+      <c r="C11" s="24"/>
+      <c r="D11" s="23">
         <v>3000000.0</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>85</v>
       </c>
       <c r="D12" s="19">
         <v>2000000.0</v>
@@ -4253,97 +4253,97 @@
     </row>
     <row r="13">
       <c r="B13" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="21" t="s">
         <v>85</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>84</v>
       </c>
       <c r="D13" s="19">
         <v>2200000.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="29">
+      <c r="C15" s="25"/>
+      <c r="D15" s="26">
         <f>SUM(D5:D13)</f>
         <v>131700000</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="M18" s="6" t="s">
+      <c r="M18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="N18" s="6" t="s">
+      <c r="N18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="O18" s="6" t="s">
+      <c r="O18" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="4"/>
       <c r="F19" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" s="8" t="s">
+      <c r="L19" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="M19" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J19" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>42</v>
-      </c>
       <c r="O19" s="8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -4354,45 +4354,45 @@
         <v>90</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="11">
+        <v>40</v>
+      </c>
+      <c r="F20" s="10">
         <f>D23</f>
         <v>53750000</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="10">
         <f>F20+F20*10%</f>
         <v>59125000</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="10">
         <f t="shared" ref="H20:O20" si="3">G20+G20*15%</f>
         <v>67993750</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="10">
         <f t="shared" si="3"/>
         <v>78192812.5</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="10">
         <f t="shared" si="3"/>
         <v>89921734.38</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="10">
         <f t="shared" si="3"/>
         <v>103409994.5</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="10">
         <f t="shared" si="3"/>
         <v>118921493.7</v>
       </c>
-      <c r="M20" s="11">
+      <c r="M20" s="10">
         <f t="shared" si="3"/>
         <v>136759717.8</v>
       </c>
-      <c r="N20" s="11">
+      <c r="N20" s="10">
         <f t="shared" si="3"/>
         <v>157273675.4</v>
       </c>
-      <c r="O20" s="11">
+      <c r="O20" s="10">
         <f t="shared" si="3"/>
         <v>180864726.7</v>
       </c>
@@ -4409,13 +4409,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="36"/>
-      <c r="F22" s="6" t="s">
+      <c r="B22" s="29"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="31"/>
+      <c r="F22" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="10">
         <f>SUM(F20:O20)</f>
         <v>1046212905</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="18"/>
-      <c r="D23" s="37">
+      <c r="D23" s="32">
         <f>C21*D21</f>
         <v>53750000</v>
       </c>
